--- a/artfynd/A 63532-2021 artfynd.xlsx
+++ b/artfynd/A 63532-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63532-2021 artfynd.xlsx
+++ b/artfynd/A 63532-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>16895882</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448392.9755887164</v>
+        <v>448393</v>
       </c>
       <c r="R2" t="n">
-        <v>7170463.626999037</v>
+        <v>7170464</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,16 +792,11 @@
         <v>16895886</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448171.6592185583</v>
+        <v>448172</v>
       </c>
       <c r="R3" t="n">
-        <v>7170169.933193154</v>
+        <v>7170170</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +857,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,16 +906,11 @@
         <v>16895887</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448225.9432922559</v>
+        <v>448226</v>
       </c>
       <c r="R4" t="n">
-        <v>7170257.306828939</v>
+        <v>7170257</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +971,9 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16895884</v>
+        <v>17225484</v>
       </c>
       <c r="B5" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,37 +1028,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörtjärnen, ca 400 m Ö om, Jmt</t>
+          <t>Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448276.684701678</v>
+        <v>448384</v>
       </c>
       <c r="R5" t="n">
-        <v>7170489.185228635</v>
+        <v>7170468</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,9 +1099,14 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>luckig gammal fjällgranskog</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1169,18 +1114,18 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # döende gammal björk</t>
+          <t>1 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1191,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16895885</v>
+        <v>16895883</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,14 +1167,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärnen, ca 200 m Ö om, Jmt</t>
+          <t>Rörtjärnen, ca 400 m Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448194.4317624765</v>
+        <v>448390</v>
       </c>
       <c r="R6" t="n">
-        <v>7170296.852322407</v>
+        <v>7170456</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,21 +1204,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1294,11 +1224,11 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10 substratenheter # grenar på levande och döda gamla granar</t>
+          <t>1 substratenheter # grov gammal granhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,15 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16895888</v>
+        <v>16895884</v>
       </c>
       <c r="B7" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,14 +1281,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnen, ca 300 m SO om, Jmt</t>
+          <t>Rörtjärnen, ca 400 m Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448356.6663109168</v>
+        <v>448277</v>
       </c>
       <c r="R7" t="n">
-        <v>7170096.042856742</v>
+        <v>7170489</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1393,21 +1318,11 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1423,11 +1338,11 @@
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>5 substratenheter # grenar på gamla granar</t>
+          <t>1 substratenheter # döende gammal björk</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1449,133 +1364,227 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17225484</v>
+        <v>16895885</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mobäcken, Jmt</t>
+          <t>Rörtjärnen, ca 200 m Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448384.0465170707</v>
+        <v>448194</v>
       </c>
       <c r="R8" t="n">
-        <v>7170468.493979327</v>
+        <v>7170297</v>
       </c>
       <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>luckig gammal fjällgranskog</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2014-07-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2014-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>10 substratenheter # grenar på levande och döda gamla granar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16895888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79486</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rörtjärnen, ca 300 m SO om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448357</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7170096</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>luckig gammal fjällgranskog</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grenar på gamla granar</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 63532-2021 artfynd.xlsx
+++ b/artfynd/A 63532-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895882</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895887</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17225484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895883</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895884</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,8 +1629,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16895885</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>